--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4072E3B2-7F24-47DD-8315-CF5BB3BD5677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4960" yWindow="4960" windowWidth="24350" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Fornitori" state="visible" r:id="rId4"/>
+    <sheet name="Fornitori" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="147">
   <si>
     <t>Ragione Sociale/Cognome</t>
   </si>
@@ -257,30 +261,258 @@
   </si>
   <si>
     <t>itasrl@pec.it</t>
+  </si>
+  <si>
+    <t>37 COMMERCIO SRL</t>
+  </si>
+  <si>
+    <t>A&amp;C DISTRIBUZIONE SRL</t>
+  </si>
+  <si>
+    <t>AERTEK LABS SRL</t>
+  </si>
+  <si>
+    <t>AF TRADING SRLS</t>
+  </si>
+  <si>
+    <t>AGE SRL</t>
+  </si>
+  <si>
+    <t>ALL TAB SRL</t>
+  </si>
+  <si>
+    <t>ALTERNA FARMACEUTICI SRL</t>
+  </si>
+  <si>
+    <t>ANITA DISTRIBUZIONE SRL</t>
+  </si>
+  <si>
+    <t>ANTON SRLS</t>
+  </si>
+  <si>
+    <t>AQUEO SRL</t>
+  </si>
+  <si>
+    <t>ARENA DISTRIBUTION SRLS</t>
+  </si>
+  <si>
+    <t>ASSO SRL</t>
+  </si>
+  <si>
+    <t>AZHAD'S ELIXIRS SRL</t>
+  </si>
+  <si>
+    <t>BAT ITALIA SPA</t>
+  </si>
+  <si>
+    <t>BE DIFFERENT SRL</t>
+  </si>
+  <si>
+    <t>BELLA VAPOR SRL</t>
+  </si>
+  <si>
+    <t>BESTBUYING SRL</t>
+  </si>
+  <si>
+    <t>BIANCOFUMO SRL</t>
+  </si>
+  <si>
+    <t>BIO-FUMO SRL</t>
+  </si>
+  <si>
+    <t>BIZZEF SRL</t>
+  </si>
+  <si>
+    <t>BR.E.MA. SRL</t>
+  </si>
+  <si>
+    <t>BRAVO SRL</t>
+  </si>
+  <si>
+    <t>Milano</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Rozzano (MI)</t>
+  </si>
+  <si>
+    <t>L’Aquila</t>
+  </si>
+  <si>
+    <t>Tivoli (RM)</t>
+  </si>
+  <si>
+    <t>Vercelli</t>
+  </si>
+  <si>
+    <t>San Giovanni Teatino</t>
+  </si>
+  <si>
+    <t>Bari</t>
+  </si>
+  <si>
+    <t>Ponsacco (PI)</t>
+  </si>
+  <si>
+    <t>Vicenza</t>
+  </si>
+  <si>
+    <t>Lanciano</t>
+  </si>
+  <si>
+    <t>Tivoli</t>
+  </si>
+  <si>
+    <t>Treviso</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>Novara</t>
+  </si>
+  <si>
+    <t>IT10407570963</t>
+  </si>
+  <si>
+    <t>IT02084420663</t>
+  </si>
+  <si>
+    <t>IT14628721008</t>
+  </si>
+  <si>
+    <t>IT02620730028</t>
+  </si>
+  <si>
+    <t>IT13245810155</t>
+  </si>
+  <si>
+    <t>IT02350620693</t>
+  </si>
+  <si>
+    <t>IT08463490725</t>
+  </si>
+  <si>
+    <t>IT14714551005</t>
+  </si>
+  <si>
+    <t>IT08659390720</t>
+  </si>
+  <si>
+    <t>IT02355820507</t>
+  </si>
+  <si>
+    <t>IT13619071007</t>
+  </si>
+  <si>
+    <t>IT08718831004</t>
+  </si>
+  <si>
+    <t>IT04196760247</t>
+  </si>
+  <si>
+    <t>IT09942150967</t>
+  </si>
+  <si>
+    <t>IT02531340698</t>
+  </si>
+  <si>
+    <t>IT15046361001</t>
+  </si>
+  <si>
+    <t>IT14630721009</t>
+  </si>
+  <si>
+    <t>IT04851870268</t>
+  </si>
+  <si>
+    <t>IT12050360019</t>
+  </si>
+  <si>
+    <t>IT02629830031</t>
+  </si>
+  <si>
+    <t>VAPORART SRL</t>
+  </si>
+  <si>
+    <t>VIA VISCONTI DI MODRONE UBERTO, 7</t>
+  </si>
+  <si>
+    <t>MILANO</t>
+  </si>
+  <si>
+    <t>IT22100P00008169</t>
+  </si>
+  <si>
+    <t>DEA FLAVOR SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VIA GALILEI, 33</t>
+  </si>
+  <si>
+    <t>LAVIS</t>
+  </si>
+  <si>
+    <t>02684230606 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF19191A"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF161616"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -295,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -306,9 +538,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -644,16 +884,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BE5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:BE29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="3" max="3" width="48.453125" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -697,7 +937,7 @@
     <col min="56" max="57" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,7 +1110,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -892,7 +1132,7 @@
       <c r="J2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>61</v>
       </c>
       <c r="L2" s="2" t="s">
@@ -917,7 +1157,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
@@ -936,7 +1176,7 @@
       <c r="J3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="5" t="s">
         <v>71</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -961,7 +1201,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -980,7 +1220,7 @@
       <c r="J4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="5" t="s">
         <v>74</v>
       </c>
       <c r="L4" s="2" t="s">
@@ -1005,7 +1245,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>75</v>
       </c>
@@ -1030,7 +1270,7 @@
       <c r="J5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="5" t="s">
         <v>79</v>
       </c>
       <c r="L5" s="2" t="s">
@@ -1058,9 +1298,280 @@
         <v>63</v>
       </c>
     </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="6">
+        <v>12812380967</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>104</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" t="s">
+        <v>141</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s">
+        <v>145</v>
+      </c>
+      <c r="K29" s="9">
+        <v>2254110220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BE5"/>
+  <autoFilter ref="A1:BE5" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -3,19 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4072E3B2-7F24-47DD-8315-CF5BB3BD5677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37C9174-8D92-4CF0-9C8F-0934315B2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="4960" windowWidth="24350" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8420" yWindow="1630" windowWidth="24350" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fornitori" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="146">
   <si>
     <t>Ragione Sociale/Cognome</t>
   </si>
@@ -441,9 +454,6 @@
   </si>
   <si>
     <t>MILANO</t>
-  </si>
-  <si>
-    <t>IT22100P00008169</t>
   </si>
   <si>
     <t>DEA FLAVOR SRL</t>
@@ -527,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -539,13 +549,12 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -899,7 +908,7 @@
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="14" width="25" customWidth="1"/>
@@ -1317,7 +1326,7 @@
         <v>105</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.35">
@@ -1327,7 +1336,7 @@
       <c r="D8" t="s">
         <v>106</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1338,7 +1347,7 @@
       <c r="D9" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1349,7 +1358,7 @@
       <c r="D10" t="s">
         <v>108</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1360,7 +1369,7 @@
       <c r="D11" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1371,7 +1380,7 @@
       <c r="D12" t="s">
         <v>104</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1382,7 +1391,7 @@
       <c r="D13" t="s">
         <v>110</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1393,7 +1402,7 @@
       <c r="D14" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1404,7 +1413,7 @@
       <c r="D15" t="s">
         <v>105</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" t="s">
         <v>126</v>
       </c>
     </row>
@@ -1415,7 +1424,7 @@
       <c r="D16" t="s">
         <v>111</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1426,7 +1435,7 @@
       <c r="D17" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1437,7 +1446,7 @@
       <c r="D18" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="K18" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1448,7 +1457,7 @@
       <c r="D19" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="K19" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1459,7 +1468,7 @@
       <c r="D20" t="s">
         <v>113</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="K20" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1470,7 +1479,7 @@
       <c r="D21" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="K21" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1481,7 +1490,7 @@
       <c r="D22" t="s">
         <v>114</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1492,7 +1501,7 @@
       <c r="D23" t="s">
         <v>105</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1503,7 +1512,7 @@
       <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1514,7 +1523,7 @@
       <c r="D25" t="s">
         <v>116</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="K25" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1525,7 +1534,7 @@
       <c r="D26" t="s">
         <v>117</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1536,7 +1545,7 @@
       <c r="D27" t="s">
         <v>118</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="K27" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1550,22 +1559,22 @@
       <c r="D28" t="s">
         <v>141</v>
       </c>
-      <c r="K28" s="8" t="s">
-        <v>142</v>
+      <c r="K28" s="7">
+        <v>8153300960</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" t="s">
         <v>144</v>
       </c>
-      <c r="D29" t="s">
-        <v>145</v>
-      </c>
-      <c r="K29" s="9">
+      <c r="K29" s="8">
         <v>2254110220</v>
       </c>
     </row>

--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37C9174-8D92-4CF0-9C8F-0934315B2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{C37C9174-8D92-4CF0-9C8F-0934315B2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9EB5A60-F443-441C-A531-DBCD2A8E4A74}"/>
   <bookViews>
-    <workbookView xWindow="8420" yWindow="1630" windowWidth="24350" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fornitori" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
   <si>
     <t>Ragione Sociale/Cognome</t>
   </si>
@@ -459,20 +459,49 @@
     <t>DEA FLAVOR SRL</t>
   </si>
   <si>
-    <t xml:space="preserve"> VIA GALILEI, 33</t>
-  </si>
-  <si>
     <t>LAVIS</t>
   </si>
   <si>
     <t>02684230606 </t>
+  </si>
+  <si>
+    <t>BRIGHTSTAR Lottery S.P.A.</t>
+  </si>
+  <si>
+    <t>DINNER LADY FAM LTD</t>
+  </si>
+  <si>
+    <t>Vapour Italia S.r.l.</t>
+  </si>
+  <si>
+    <t>IT02956690305</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF19191A"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>VIA STIRIA 45</t>
+    </r>
+  </si>
+  <si>
+    <t>Udine</t>
+  </si>
+  <si>
+    <t>VIA GALILEI, 33</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +539,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF474747"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF627D98"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF19191A"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -537,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -555,6 +602,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -897,18 +946,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BE29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BE32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="48.453125" customWidth="1"/>
+    <col min="3" max="3" width="48.42578125" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20.81640625" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="14" width="25" customWidth="1"/>
@@ -946,7 +995,7 @@
     <col min="56" max="57" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1168,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -1166,7 +1215,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
@@ -1210,7 +1259,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -1254,7 +1303,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>75</v>
       </c>
@@ -1307,7 +1356,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1318,7 +1367,7 @@
         <v>12812380967</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -1326,10 +1375,10 @@
         <v>105</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1340,7 +1389,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -1351,7 +1400,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1362,7 +1411,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1373,7 +1422,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -1384,7 +1433,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -1395,7 +1444,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -1406,7 +1455,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>91</v>
       </c>
@@ -1417,7 +1466,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -1428,7 +1477,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>93</v>
       </c>
@@ -1439,7 +1488,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -1450,7 +1499,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>95</v>
       </c>
@@ -1461,7 +1510,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -1472,7 +1521,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>97</v>
       </c>
@@ -1483,7 +1532,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>98</v>
       </c>
@@ -1494,7 +1543,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -1505,7 +1554,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -1516,7 +1565,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -1527,7 +1576,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -1538,7 +1587,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -1549,7 +1598,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>139</v>
       </c>
@@ -1563,19 +1612,49 @@
         <v>8153300960</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" t="s">
         <v>143</v>
-      </c>
-      <c r="D29" t="s">
-        <v>144</v>
       </c>
       <c r="K29" s="8">
         <v>2254110220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30">
+        <v>16866691005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="K31" s="9">
+        <v>10213240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" t="s">
+        <v>150</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{C37C9174-8D92-4CF0-9C8F-0934315B2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9EB5A60-F443-441C-A531-DBCD2A8E4A74}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{C37C9174-8D92-4CF0-9C8F-0934315B2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF084F6-1197-4DC4-89CC-C6FBDE5D1FD0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="155">
   <si>
     <t>Ragione Sociale/Cognome</t>
   </si>
@@ -477,31 +477,29 @@
     <t>IT02956690305</t>
   </si>
   <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF19191A"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>VIA STIRIA 45</t>
-    </r>
-  </si>
-  <si>
     <t>Udine</t>
   </si>
   <si>
     <t>VIA GALILEI, 33</t>
+  </si>
+  <si>
+    <t>Svapo &amp; Basta</t>
+  </si>
+  <si>
+    <t>Via Gandhi 9</t>
+  </si>
+  <si>
+    <t>Samarate</t>
+  </si>
+  <si>
+    <t>VIA STIRIA 45</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,6 +511,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -528,34 +527,52 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF19191A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF161616"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1B1B1B"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF474747"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF627D98"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF19191A"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -584,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -596,14 +613,25 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -619,6 +647,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -946,7 +978,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BE32"/>
+  <dimension ref="A1:BE33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1190,7 +1222,7 @@
       <c r="J2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>61</v>
       </c>
       <c r="L2" s="2" t="s">
@@ -1234,7 +1266,7 @@
       <c r="J3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>71</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -1278,7 +1310,7 @@
       <c r="J4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>74</v>
       </c>
       <c r="L4" s="2" t="s">
@@ -1328,7 +1360,7 @@
       <c r="J5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>79</v>
       </c>
       <c r="L5" s="2" t="s">
@@ -1363,7 +1395,7 @@
       <c r="D6" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <v>12812380967</v>
       </c>
     </row>
@@ -1374,7 +1406,7 @@
       <c r="D7" t="s">
         <v>105</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1385,7 +1417,7 @@
       <c r="D8" t="s">
         <v>106</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1396,7 +1428,7 @@
       <c r="D9" t="s">
         <v>107</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="6" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1407,7 +1439,7 @@
       <c r="D10" t="s">
         <v>108</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="6" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1418,7 +1450,7 @@
       <c r="D11" t="s">
         <v>109</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1429,7 +1461,7 @@
       <c r="D12" t="s">
         <v>104</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="6" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1440,7 +1472,7 @@
       <c r="D13" t="s">
         <v>110</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="6" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1451,7 +1483,7 @@
       <c r="D14" t="s">
         <v>111</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="6" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1462,7 +1494,7 @@
       <c r="D15" t="s">
         <v>105</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="6" t="s">
         <v>126</v>
       </c>
     </row>
@@ -1473,7 +1505,7 @@
       <c r="D16" t="s">
         <v>111</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="6" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1484,7 +1516,7 @@
       <c r="D17" t="s">
         <v>112</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="6" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1495,7 +1527,7 @@
       <c r="D18" t="s">
         <v>105</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1506,7 +1538,7 @@
       <c r="D19" t="s">
         <v>105</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="6" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1517,7 +1549,7 @@
       <c r="D20" t="s">
         <v>113</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="6" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1528,7 +1560,7 @@
       <c r="D21" t="s">
         <v>104</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1539,7 +1571,7 @@
       <c r="D22" t="s">
         <v>114</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="6" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1550,7 +1582,7 @@
       <c r="D23" t="s">
         <v>105</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="6" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1561,7 +1593,7 @@
       <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="6" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1572,7 +1604,7 @@
       <c r="D25" t="s">
         <v>116</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="6" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1583,7 +1615,7 @@
       <c r="D26" t="s">
         <v>117</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="6" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1594,7 +1626,7 @@
       <c r="D27" t="s">
         <v>118</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="6" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1608,7 +1640,7 @@
       <c r="D28" t="s">
         <v>141</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="8">
         <v>8153300960</v>
       </c>
     </row>
@@ -1618,12 +1650,12 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="9">
         <v>2254110220</v>
       </c>
     </row>
@@ -1631,7 +1663,7 @@
       <c r="A30" t="s">
         <v>145</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="6">
         <v>16866691005</v>
       </c>
     </row>
@@ -1639,7 +1671,7 @@
       <c r="A31" t="s">
         <v>146</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="10">
         <v>10213240</v>
       </c>
     </row>
@@ -1647,14 +1679,28 @@
       <c r="A32" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
         <v>149</v>
       </c>
-      <c r="D32" t="s">
-        <v>150</v>
-      </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="11" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" t="s">
+        <v>153</v>
+      </c>
+      <c r="K33" s="6">
+        <v>2259750129</v>
       </c>
     </row>
   </sheetData>

--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{C37C9174-8D92-4CF0-9C8F-0934315B2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF084F6-1197-4DC4-89CC-C6FBDE5D1FD0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0970F-F0C0-4150-85B8-FD6F4B605C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9980" yWindow="3070" windowWidth="20000" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fornitori" sheetId="1" r:id="rId1"/>
@@ -647,10 +647,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -979,17 +975,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:BE33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="48.42578125" customWidth="1"/>
+    <col min="3" max="3" width="48.453125" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="14" width="25" customWidth="1"/>
@@ -1027,7 +1023,7 @@
     <col min="56" max="57" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1196,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -1247,18 +1243,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>62</v>
@@ -1267,10 +1263,10 @@
         <v>63</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>65</v>
@@ -1291,80 +1287,38 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4" s="6">
+        <v>16866691005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="J5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>65</v>
@@ -1372,9 +1326,6 @@
       <c r="N5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="Z5" s="3">
         <v>0</v>
       </c>
@@ -1388,323 +1339,368 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="K7" s="6">
+        <v>2259750129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>82</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K8" s="7">
         <v>12812380967</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>83</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>105</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>84</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>106</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>85</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D11" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>86</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" t="s">
         <v>108</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>87</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>88</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>104</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K14" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>89</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>110</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K15" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>111</v>
       </c>
       <c r="K16" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>93</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K19" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>94</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D20" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K20" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>95</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K21" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>96</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" t="s">
         <v>113</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K22" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>97</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K23" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>98</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" t="s">
         <v>114</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K24" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>99</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D25" t="s">
         <v>105</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K25" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>100</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D26" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K26" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>101</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>116</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K27" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>102</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>117</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K28" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>103</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
         <v>118</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K29" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D30" t="s">
         <v>141</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K30" s="8">
         <v>8153300960</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D31" t="s">
         <v>143</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K31" s="9">
         <v>2254110220</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>145</v>
-      </c>
-      <c r="K30" s="6">
-        <v>16866691005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>146</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K32" s="10">
         <v>10213240</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>149</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K33" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D33" t="s">
-        <v>153</v>
-      </c>
-      <c r="K33" s="6">
-        <v>2259750129</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BE5" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BE6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0970F-F0C0-4150-85B8-FD6F4B605C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A2954C-21D2-45D2-98C8-6AC3EB036153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9980" yWindow="3070" windowWidth="20000" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7310" yWindow="7360" windowWidth="24470" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fornitori" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="158">
   <si>
     <t>Ragione Sociale/Cognome</t>
   </si>
@@ -493,6 +493,15 @@
   </si>
   <si>
     <t>VIA STIRIA 45</t>
+  </si>
+  <si>
+    <t>FERRERO S.P.A.</t>
+  </si>
+  <si>
+    <t>VIA PANCALIERI 1</t>
+  </si>
+  <si>
+    <t>CASALGRASSO (CN)</t>
   </si>
 </sst>
 </file>
@@ -974,7 +983,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BE33"/>
+  <dimension ref="A1:BE34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1699,6 +1708,20 @@
         <v>148</v>
       </c>
     </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" t="s">
+        <v>157</v>
+      </c>
+      <c r="K34">
+        <v>2106920040</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:BE6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExportFornitori.xlsx
+++ b/ExportFornitori.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A2954C-21D2-45D2-98C8-6AC3EB036153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB3A451-9500-47D8-8E66-12E000085AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7310" yWindow="7360" windowWidth="24470" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="160">
   <si>
     <t>Ragione Sociale/Cognome</t>
   </si>
@@ -502,6 +502,12 @@
   </si>
   <si>
     <t>CASALGRASSO (CN)</t>
+  </si>
+  <si>
+    <t>Regioni</t>
+  </si>
+  <si>
+    <t>Citta</t>
   </si>
 </sst>
 </file>
@@ -983,7 +989,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BE34"/>
+  <dimension ref="A1:BG34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1032,7 +1038,7 @@
     <col min="56" max="57" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1204,8 +1210,14 @@
       <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="BF1" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -1252,7 +1264,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>73</v>
       </c>
@@ -1296,7 +1308,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -1304,7 +1316,7 @@
         <v>16866691005</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>67</v>
       </c>
@@ -1348,7 +1360,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>75</v>
       </c>
@@ -1401,7 +1413,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -1415,7 +1427,7 @@
         <v>2259750129</v>
       </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1426,7 +1438,7 @@
         <v>12812380967</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1437,7 +1449,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -1448,7 +1460,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -1459,7 +1471,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -1470,7 +1482,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1481,7 +1493,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -1492,7 +1504,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1503,7 +1515,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>90</v>
       </c>
